--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-04-2026.xlsx
@@ -558,12 +558,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>£11.78</t>
+          <t>£13.55</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£13.12</t>
+          <t>£13.13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>£13.85</t>
+          <t>£15.93</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>£17.09</t>
+          <t>£19.65</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>£18.20</t>
+          <t>£20.93</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£19.68</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>£22.59</t>
+          <t>£25.98</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>£25.29</t>
+          <t>£29.08</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£27.2</t>
+          <t>£27.20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>£25.29</t>
+          <t>£29.08</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>£28.80</t>
+          <t>£33.12</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>£29.14</t>
+          <t>£29.91</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>£31.50</t>
+          <t>£36.23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>£30.43</t>
+          <t>£34.14</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>£30.65</t>
+          <t>£35.25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>£31.95</t>
+          <t>£32.78</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>£38.76</t>
+          <t>£39.78</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>£37.65</t>
+          <t>£43.30</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>£38.75</t>
+          <t>£40.75</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>£45.30</t>
+          <t>£52.10</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£54.92</t>
+          <t>£54.93</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>£52.72</t>
+          <t>£47.05</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>£45.98</t>
+          <t>£52.88</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>£45.93</t>
+          <t>£47.80</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>£46.39</t>
+          <t>£53.35</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£51.2</t>
+          <t>£51.20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>£47.37</t>
+          <t>£48.74</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>£855.60</t>
+          <t>£983.94</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>£1008.0</t>
+          <t>£1008.00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>£1,074.10</t>
+          <t>£1,235.22</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>£1209.7</t>
+          <t>£1209.70</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>£32.84</t>
+          <t>£37.77</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>£39.75</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationuk.co.uk', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>£40.00</t>
+          <t>£46.00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>£43.92</t>
+          <t>£50.51</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>£51.23</t>
+          <t>£58.91</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>£45.01</t>
+          <t>£51.00</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>£54.59</t>
+          <t>£62.78</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>£58.95</t>
+          <t>£67.79</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>£100.4</t>
+          <t>£100.40</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>£53.96</t>
+          <t>£62.05</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>£1378.24</t>
+          <t>£1584.96</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>£1376.8</t>
+          <t>£1376.80</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>£1534.56</t>
+          <t>£1764.8</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>£1467.36</t>
+          <t>£1687.52</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>£1571.2</t>
+          <t>£1571.20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-04-2026.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£13.13</t>
+          <t>£20.11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>£12.30</t>
+          <t>£12.62</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>£15.08</t>
+          <t>£53.85</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>£15.21</t>
+          <t>£15.61</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£19.34</t>
+          <t>£26.73</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>£18.48</t>
+          <t>£18.18</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£19.68</t>
+          <t>£46.31</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>£19.37</t>
+          <t>£19.04</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>£25.22</t>
+          <t>£26.23</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>£24.93</t>
+          <t>£24.52</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£27.20</t>
+          <t>£48.46</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>£26.09</t>
+          <t>£26.10</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£27.62</t>
+          <t>£36.61</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>£26.80</t>
+          <t>£27.51</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1177,19 +1177,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>£29.15</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>£29.15</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>£29.15</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>£29.74</t>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>£31.48</t>
+          <t>£12.57</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>£34.47</t>
+          <t>£10.94</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£32.08</t>
+          <t>£94.34</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£49.11</t>
+          <t>£10.94</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>£41.23</t>
+          <t>£26.73</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£54.93</t>
+          <t>£94.34</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£55.57</t>
+          <t>£64.62</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£51.20</t>
+          <t>£20.11</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>£1008.00</t>
+          <t>£131.30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>£1209.70</t>
+          <t>£272.00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>£43.93</t>
+          <t>£53.85</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>£33.62</t>
+          <t>£31.77</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationuk.co.uk', port=443): Read timed out. (read timeout=30)</t>
+          <t>£39.75</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>£55.57</t>
+          <t>£71.30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>£37.68</t>
+          <t>£38.66</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>£58.15</t>
+          <t>£85.42</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>£40.37</t>
+          <t>£41.43</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>£51.00</t>
+          <t>£49.71</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>£92.31</t>
+          <t>£288.57</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>£100.40</t>
+          <t>£275.73</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>£96.25</t>
+          <t>£274.65</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>£1376.80</t>
+          <t>£1930.40</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>£1653.33</t>
+          <t>£2138.67</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>£1571.20</t>
+          <t>£1473.07</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>£1790.88</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
     </row>
